--- a/RF3/RepDays-K-medoids.xlsx
+++ b/RF3/RepDays-K-medoids.xlsx
@@ -442,42 +442,42 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3479452054794521</v>
+        <v>0.0410958904109589</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>243</v>
+        <v>33</v>
       </c>
       <c r="B3" t="n">
-        <v>0.1287671232876712</v>
+        <v>0.263013698630137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1287671232876712</v>
+        <v>0.08767123287671233</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1780821917808219</v>
+        <v>0.3424657534246575</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2164383561643836</v>
+        <v>0.2657534246575343</v>
       </c>
     </row>
   </sheetData>
